--- a/Collections/EURO/Spain/#EURO#Spain#Commemorative#[2005-present]#UNC.xlsx
+++ b/Collections/EURO/Spain/#EURO#Spain#Commemorative#[2005-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Spain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD268A6-17AF-48BF-91E4-41EA3BFF7331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D62D3CE-5026-4472-8EFE-CF58104F3442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -159,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="77">
   <si>
     <t>Year</t>
   </si>
@@ -384,6 +387,12 @@
   </si>
   <si>
     <t>Subtype_2#Special_marks_1</t>
+  </si>
+  <si>
+    <t>Poblet Monastery</t>
+  </si>
+  <si>
+    <t>Reform of Article 49 of the Spanish Constitution</t>
   </si>
 </sst>
 </file>
@@ -697,7 +706,23 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -824,9 +849,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1095,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="13" customWidth="1"/>
@@ -1981,7 +2006,61 @@
         <v>1</v>
       </c>
       <c r="I32" s="11" t="str">
-        <f t="shared" ref="I32" si="9">IF(OR(AND(H32&gt;1,H32&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I32:I33" si="9">IF(OR(AND(H32&gt;1,H32&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="8"/>
+      <c r="G33" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H33" s="10">
+        <v>0</v>
+      </c>
+      <c r="I33" s="11" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="8"/>
+      <c r="G34" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="11" t="str">
+        <f t="shared" ref="I34" si="10">IF(OR(AND(H34&gt;1,H34&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -1993,11 +2072,45 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="H3 H9:H24 H5 H7">
+    <cfRule type="containsText" dxfId="16" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9:H24 H3 H5 H7">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="15" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
     <cfRule type="containsText" dxfId="14" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9:H24 H3 H5 H7">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2009,29 +2122,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="containsText" dxfId="13" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
+  <conditionalFormatting sqref="H25">
+    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2043,12 +2139,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
+  <conditionalFormatting sqref="H26">
+    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="containsText" dxfId="11" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H27">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2060,12 +2173,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
+  <conditionalFormatting sqref="H28">
     <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2077,12 +2190,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
+  <conditionalFormatting sqref="H29">
     <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H29">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2094,12 +2207,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
+  <conditionalFormatting sqref="H30">
     <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2111,12 +2224,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
+  <conditionalFormatting sqref="H31">
     <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H29">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2128,12 +2241,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
+  <conditionalFormatting sqref="H8">
     <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2145,12 +2258,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
+  <conditionalFormatting sqref="H32">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2162,12 +2275,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8">
+  <conditionalFormatting sqref="H33">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2179,12 +2292,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
+  <conditionalFormatting sqref="H34">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
